--- a/case-logs/ANESTHESIA_(PHYSICIAN)_CASE_LOG_TEMPLATE_July_8_2026.xlsx
+++ b/case-logs/ANESTHESIA_(PHYSICIAN)_CASE_LOG_TEMPLATE_July_8_2026.xlsx
@@ -15,11 +15,11 @@
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Applicant Information" sheetId="2" r:id="rId2"/>
-    <sheet name="Adult Anesthesia" sheetId="3" r:id="rId3"/>
-    <sheet name="Pediatric Anesthesia" sheetId="4" r:id="rId4"/>
+    <sheet name="Core (2 years and older)" sheetId="3" r:id="rId3"/>
+    <sheet name="Pediatric (2 months and older)" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Adult Anesthesia'!$B$1:$H$1644</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Core (2 years and older)'!$B$1:$H$1644</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -474,7 +474,7 @@
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Complete the appropriate sections (tabs) of the workbook corresponding to the privilege categories being requested (e.g., Adult Anesthesia, Pediatric Anesthesia).</a:t>
+            <a:t>Complete the appropriate sections (tabs) of the workbook corresponding to the privilege categories being requested (e.g., Core (2 years and older), Pediatric (2 months and older)).</a:t>
           </a:r>
         </a:p>
         <a:p>

--- a/case-logs/ANESTHESIA_(PHYSICIAN)_CASE_LOG_TEMPLATE_July_8_2026.xlsx
+++ b/case-logs/ANESTHESIA_(PHYSICIAN)_CASE_LOG_TEMPLATE_July_8_2026.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Applicant Information" sheetId="2" r:id="rId2"/>
     <sheet name="Core (2 years and older)" sheetId="3" r:id="rId3"/>
-    <sheet name="Pediatric (2 months and older)" sheetId="4" r:id="rId4"/>
+    <sheet name="Pediatric (2 months to 2 years)" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Core (2 years and older)'!$B$1:$H$1644</definedName>
@@ -474,7 +474,7 @@
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Complete the appropriate sections (tabs) of the workbook corresponding to the privilege categories being requested (e.g., Core (2 years and older), Pediatric (2 months and older)).</a:t>
+            <a:t>Complete the appropriate sections (tabs) of the workbook corresponding to the privilege categories being requested (e.g., Core (2 years and older), Pediatric (2 months to 2 years)).</a:t>
           </a:r>
         </a:p>
         <a:p>

--- a/case-logs/ANESTHESIA_(PHYSICIAN)_CASE_LOG_TEMPLATE_July_8_2026.xlsx
+++ b/case-logs/ANESTHESIA_(PHYSICIAN)_CASE_LOG_TEMPLATE_July_8_2026.xlsx
@@ -15,11 +15,11 @@
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Applicant Information" sheetId="2" r:id="rId2"/>
-    <sheet name="Core (2 years and older)" sheetId="3" r:id="rId3"/>
-    <sheet name="Pediatric (2 months to 2 years)" sheetId="4" r:id="rId4"/>
+    <sheet name="2 months and older" sheetId="3" r:id="rId3"/>
+    <sheet name="Any age" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Core (2 years and older)'!$B$1:$H$1644</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 months and older'!$B$1:$H$1644</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -474,7 +474,7 @@
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Complete the appropriate sections (tabs) of the workbook corresponding to the privilege categories being requested (e.g., Core (2 years and older), Pediatric (2 months to 2 years)).</a:t>
+            <a:t>Complete the appropriate sections (tabs) of the workbook corresponding to the privilege categories being requested (e.g., 2 months and older, Any age).</a:t>
           </a:r>
         </a:p>
         <a:p>
